--- a/Example Product Sheet.xlsx
+++ b/Example Product Sheet.xlsx
@@ -141,7 +141,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,6 +152,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -204,40 +210,40 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="7" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -574,7 +580,7 @@
     <col min="15" max="15" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -591,7 +597,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -608,7 +614,7 @@
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -625,7 +631,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -642,7 +648,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -659,7 +665,7 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="5" t="s">
         <v>0</v>
       </c>
@@ -706,7 +712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="20.25">
       <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
@@ -729,7 +735,7 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="20.25">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -752,7 +758,7 @@
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="20.25">
       <c r="A9" s="8" t="s">
         <v>14</v>
       </c>
@@ -775,7 +781,7 @@
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="20.25">
       <c r="A10" s="8" t="s">
         <v>17</v>
       </c>
@@ -796,7 +802,7 @@
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="20.25">
       <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
@@ -817,7 +823,7 @@
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="20.25">
       <c r="A12" s="8" t="s">
         <v>21</v>
       </c>
@@ -838,7 +844,7 @@
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="20.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="8" t="s">
@@ -857,7 +863,7 @@
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="20.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="8" t="s">
@@ -876,7 +882,7 @@
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -893,7 +899,7 @@
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -910,7 +916,7 @@
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
@@ -929,7 +935,7 @@
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
       <c r="A18" s="8" t="s">
         <v>14</v>
       </c>
@@ -968,7 +974,7 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -985,7 +991,7 @@
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1002,7 +1008,7 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
